--- a/src/attributions/attributions_ig_traj_314.xlsx
+++ b/src/attributions/attributions_ig_traj_314.xlsx
@@ -999,34 +999,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.1421825698540194</v>
+        <v>0.0994740683196316</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1285335921211886</v>
+        <v>-0.2120682156804988</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09799760050710242</v>
+        <v>0.0398435463703125</v>
       </c>
       <c r="F2" t="n">
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1512598411973364</v>
+        <v>0.0688338266778451</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1035,25 +1035,25 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03947837465300065</v>
+        <v>-0.2279995634975857</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06157238441841095</v>
+        <v>-0.006085476264122433</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03503361503434215</v>
+        <v>-0.03111586160562456</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -1062,40 +1062,40 @@
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1137750778042988</v>
+        <v>-0.07921459322253484</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09919443329398833</v>
+        <v>-0.05693190142025826</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.08451020001721837</v>
+        <v>0.0192147390838971</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.04872316865413782</v>
+        <v>0.07637895379576093</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.01936034462616416</v>
+        <v>0.1860789840773809</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -1104,49 +1104,49 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.0361793093830545</v>
+        <v>0.01610478693152976</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.03305684023071611</v>
+        <v>-0.1899078963215663</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.0772390132790992</v>
+        <v>0.06713973966130993</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
         <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1303383044105264</v>
+        <v>-0.06818867464834112</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.09581288633160839</v>
+        <v>-0.3859762873766177</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2787822074638125</v>
+        <v>-0.0445785782956578</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
@@ -1161,46 +1161,46 @@
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.1943954045014266</v>
+        <v>0.1654538229682972</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.03070478785801391</v>
+        <v>0.1922042532012535</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.04153180979682465</v>
+        <v>0.1512645064240116</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0765525857429586</v>
+        <v>0.03446828623071686</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0479400578944628</v>
+        <v>0.02130803773370922</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1886285444255066</v>
+        <v>-0.1501129309799056</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
@@ -1209,25 +1209,25 @@
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.04184780835903857</v>
+        <v>-0.07574731185243343</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01435889594339419</v>
+        <v>-0.2879789854966622</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1452707118184026</v>
+        <v>-0.03767073502589709</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,94 +1236,94 @@
         <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.03618838348701425</v>
+        <v>-0.05975524094861706</v>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.01416192217276806</v>
+        <v>0.1397444732561172</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.03796488293523147</v>
+        <v>-0.01602704599736187</v>
       </c>
       <c r="CI2" t="n">
         <v>0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.05040047577711786</v>
+        <v>-0.0009125708099633541</v>
       </c>
       <c r="CN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.1123030998058894</v>
+        <v>0.1024702028232764</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.08760851356791942</v>
+        <v>-0.05005669711245266</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.01496634220186168</v>
+        <v>-0.04566924314707472</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="n">
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.01724506530483497</v>
+        <v>0.137365025263022</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.02724228930838036</v>
+        <v>0.003615431114672071</v>
       </c>
       <c r="DA2" t="n">
         <v>-0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.02696971579277541</v>
+        <v>-0.007553904996398559</v>
       </c>
       <c r="DF2" t="n">
         <v>-0</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.09151145698031155</v>
+        <v>0.1111398246144402</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.0449451897890506</v>
+        <v>-0.03884046849173635</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
@@ -1347,22 +1347,22 @@
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0.06362288892862403</v>
+        <v>-0.06049354782675222</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0552113184693578</v>
+        <v>0.01373901379520496</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.1067814253989213</v>
+        <v>0.04485800486909329</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1371,82 +1371,82 @@
         <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.07121658644081263</v>
+        <v>0.01115614313286294</v>
       </c>
       <c r="DX2" t="n">
         <v>-0</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.03355830707122646</v>
+        <v>0.04816350328604282</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.1012391355342815</v>
+        <v>0.0120370782672157</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.03403087358055072</v>
+        <v>-0.09347189611509024</v>
       </c>
       <c r="EG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.04054620994193478</v>
+        <v>0.1280709267839789</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0272775782971152</v>
+        <v>0.02078836714309756</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.006900665209931929</v>
+        <v>0.03029223414145254</v>
       </c>
       <c r="EP2" t="n">
         <v>0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.04158658537213703</v>
+        <v>0.1580189304273162</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03649618659852212</v>
+        <v>0.01904658674794507</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
@@ -1458,34 +1458,34 @@
         <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0.01987577799332894</v>
+        <v>-0.05432077209382965</v>
       </c>
       <c r="EY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.001465266569131017</v>
+        <v>0.1729425115003777</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.03597672400863517</v>
+        <v>-0.006995344590317376</v>
       </c>
       <c r="FC2" t="n">
         <v>0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0.05443888042460984</v>
+        <v>0.01513123097459413</v>
       </c>
       <c r="FH2" t="n">
         <v>0</v>
@@ -1494,10 +1494,10 @@
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.03827840429617509</v>
+        <v>0.0904147835944563</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1917332662588294</v>
+        <v>0.1569669647960137</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
@@ -1506,40 +1506,40 @@
         <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.008763025068204434</v>
+        <v>-0.01229997499017948</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.04878807284918669</v>
+        <v>0.233580845573438</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.07981827715379639</v>
+        <v>0.09978617480528039</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
         <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.02828101740985203</v>
+        <v>0.0169434313430052</v>
       </c>
       <c r="FZ2" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.03992599779712361</v>
+        <v>0.2526081026918165</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
@@ -2709,22 +2709,22 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3550222341779681</v>
+        <v>0.2794380551008827</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1083491228102015</v>
+        <v>-0.1170501608429114</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02908856710364221</v>
+        <v>-0.02588559618840463</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2733,25 +2733,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.215101049932739</v>
+        <v>0.2734888423974672</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1364174326713908</v>
+        <v>-0.1699185256802883</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02197882413088149</v>
+        <v>-0.06421975401209365</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2763,70 +2763,70 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1037103856652867</v>
+        <v>0.07601695363031054</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.009072630986332608</v>
+        <v>-0.0374140890966464</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1133123395851955</v>
+        <v>-0.06118475312755697</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04178221268168193</v>
+        <v>-0.05642154792733298</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.008072132093618175</v>
+        <v>-0.1301840256365648</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01907041006316944</v>
+        <v>-0.04842000122698775</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.00161127804669002</v>
+        <v>0.09009473535156166</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.0668150588862086</v>
+        <v>-0.06166584551772936</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.05262218079517091</v>
+        <v>0.08363018868172953</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2844,25 +2844,25 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3913604664885948</v>
+        <v>0.2944090861970797</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.03217396434085266</v>
+        <v>-0.04304634099101542</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1184177801912282</v>
+        <v>-0.2123630123406504</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
@@ -2871,43 +2871,43 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.05234163817244458</v>
+        <v>-0.002592701769803417</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1417034381362608</v>
+        <v>-0.04770620050694104</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.08773643566622721</v>
+        <v>-0.01459789332999627</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1029754828596132</v>
+        <v>-0.01485641515893353</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.06140422103252366</v>
+        <v>0.03457310921258396</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1810537724234016</v>
+        <v>0.07998337122247631</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
@@ -2925,49 +2925,49 @@
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1398636219228022</v>
+        <v>0.1480835421864099</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.02402296462042639</v>
+        <v>-0.07113655314907745</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.06699368672365612</v>
+        <v>-0.04099055208460327</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1010068281367278</v>
+        <v>-0.1277288506461092</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.006943772630448844</v>
+        <v>0.0886394368576513</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.01640247756530192</v>
+        <v>0.01491592793608677</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2979,43 +2979,43 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.007307932197828391</v>
+        <v>-0.05297797580014496</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.09726852286456415</v>
+        <v>0.1569201228166521</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.05849722662840842</v>
+        <v>0.0520506221724979</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.07138465848474622</v>
+        <v>-0.1285675965906265</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.02839228966104916</v>
+        <v>0.1003535267147862</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.02041304324762506</v>
+        <v>0.02095636122902464</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.03400962160302536</v>
+        <v>-0.07158131865464012</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.044686101213306</v>
+        <v>0.01763025064962886</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07895636551591184</v>
+        <v>-0.08549514861256242</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3054,31 +3054,31 @@
         <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.07834602596130223</v>
+        <v>-0.05169833830805638</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01619998304896742</v>
+        <v>-0.05751890080363038</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.04311651495662873</v>
+        <v>-0.04649323355726608</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
@@ -3087,19 +3087,19 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.08776206315411667</v>
+        <v>-0.06556994403597717</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.02149343577099977</v>
+        <v>0.06124801769434023</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01460154835553401</v>
+        <v>0.009468638986118617</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3108,22 +3108,22 @@
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.09126386774163817</v>
+        <v>-0.1001153234741274</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.01085087572118044</v>
+        <v>0.05371115168186314</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.05686299998446913</v>
+        <v>0.05422401167727176</v>
       </c>
       <c r="EK5" t="n">
         <v>0</v>
@@ -3132,31 +3132,31 @@
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.007385145400823924</v>
+        <v>-0.04115821789760386</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0008256724344309547</v>
+        <v>0.03528025093265894</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.03584764735390998</v>
+        <v>-0.003596394124145008</v>
       </c>
       <c r="ET5" t="n">
         <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,19 +3165,19 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.0718236674784801</v>
+        <v>-0.1369829168410536</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.01336727975048232</v>
+        <v>0.1239411576031096</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01196032903680531</v>
+        <v>-0.00208795841478015</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
@@ -3186,7 +3186,7 @@
         <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
@@ -3195,16 +3195,16 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.05552623381900759</v>
+        <v>0.09605706773439504</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.01475234502649754</v>
+        <v>0.08690059617371414</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0330606517760535</v>
+        <v>0.01420072077130205</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3216,28 +3216,28 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.05701629621533687</v>
+        <v>0.05331141387813949</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.006399970247550475</v>
+        <v>0.1484054985982735</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.06151104926463345</v>
+        <v>-0.05477065776719019</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
@@ -3246,31 +3246,31 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.06838052250279232</v>
+        <v>-0.08143748785181208</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.133106598021819</v>
+        <v>0.06359545714768568</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.09563754557912194</v>
+        <v>0.2035230091630711</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,25 +3287,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02611365929440618</v>
+        <v>-0.01935811312690509</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.05314649407367218</v>
+        <v>-0.129337786704209</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07254357021058531</v>
+        <v>0.2330765167328967</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02043659777032576</v>
+        <v>-0.08411027866919164</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.04129768030222469</v>
+        <v>-0.1457452821131813</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3326,94 +3326,94 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003921663091310741</v>
+        <v>0.07008604165056616</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.008223461075364652</v>
+        <v>-0.08637968473348892</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01070041884961261</v>
+        <v>-0.007363751522846135</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.009554807050206018</v>
+        <v>-0.04348317971943364</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01800060657805181</v>
+        <v>-0.1789573063835479</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002052330334881764</v>
+        <v>0.03124830101195808</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.001101783037154199</v>
+        <v>0.02938600813493609</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01295020696859269</v>
+        <v>-0.03953623772530148</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.01058373235862832</v>
+        <v>-0.006483339816534496</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.08597842185070995</v>
+        <v>0.2486797218330832</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,67 +3422,67 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01442821779413454</v>
+        <v>-0.2041513846403742</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01661329247217291</v>
+        <v>-0.111812386111966</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02875714638025674</v>
+        <v>0.00703282963823524</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03183951991102266</v>
+        <v>-0.0001325680973935406</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.04895204489309409</v>
+        <v>-0.0654036154938341</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
         <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
         <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03490307986516374</v>
+        <v>0.02850139853763939</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02095167787504897</v>
+        <v>0.07956757933849821</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01725614772929692</v>
+        <v>0.04013674477737337</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3491,22 +3491,22 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.03387061090312539</v>
+        <v>0.1252758039911469</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.006005056340848221</v>
+        <v>-0.04280948568612001</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-4.290481660439534e-05</v>
+        <v>-0.09382301054907581</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3515,28 +3515,28 @@
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.01978106900244861</v>
+        <v>-0.07076330381539533</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002598558183607901</v>
+        <v>0.01311885632082329</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01960855587048792</v>
+        <v>0.07255806851135846</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>-0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0004836168814503677</v>
+        <v>-0.03462532251190015</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
@@ -3557,172 +3557,172 @@
         <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.004868521266502704</v>
+        <v>0.07436138021256661</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01502390354756369</v>
+        <v>0.06673127602801468</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.01566497053442286</v>
+        <v>-0.07316862563077985</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.004745245264798076</v>
+        <v>0.01332790550664638</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01971768244066367</v>
+        <v>0.09392171521893777</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0134066732182603</v>
+        <v>-0.03294924058457956</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.02277180598826387</v>
+        <v>-0.0754726657672526</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.009396252256845506</v>
+        <v>0.06005058649780495</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.008809592822506778</v>
+        <v>0.0005530129588145307</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01597183302846076</v>
+        <v>-0.05075673311655277</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.005513089456434641</v>
+        <v>0.01823067714340409</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.03775841033851258</v>
+        <v>-0.00897062821590615</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ6" t="n">
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01393831837297099</v>
+        <v>-0.006609925751076888</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.01278473356407653</v>
+        <v>0.05456120389101134</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.02137815282671264</v>
+        <v>-0.03587438318974277</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.004675475617747</v>
+        <v>0.01245348567230978</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01570128737287158</v>
+        <v>0.02043795240354885</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.01033508862550276</v>
+        <v>-0.02093924044087198</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.006595333825214555</v>
+        <v>-0.01141907191455018</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0007459359622123896</v>
+        <v>0.09208927298394531</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.01588368567221396</v>
+        <v>-0.08197503073382482</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,43 +3746,43 @@
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.009042815344744073</v>
+        <v>-0.006752174548465219</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.02370262360764342</v>
+        <v>0.06457554606341855</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.02618138370873152</v>
+        <v>0.1251276861949162</v>
       </c>
       <c r="FI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.009865117611435418</v>
+        <v>-0.03065172012601772</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01487797117935015</v>
+        <v>0.09690274732255175</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.001937042286958931</v>
+        <v>0.03573891897722017</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
@@ -3800,40 +3800,40 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.01845202975183627</v>
+        <v>-0.06488853688168526</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.008634514075669827</v>
+        <v>-0.06480327278056042</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.005401869187417259</v>
+        <v>-0.03747200684849918</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.00587007605804729</v>
+        <v>0.0963788206481023</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
         <v>-0</v>
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4298655694601202</v>
+        <v>0.2244454568786266</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1379925970400744</v>
+        <v>-0.09656103039553621</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02898728881564427</v>
+        <v>-0.03407312815536694</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2806773974746499</v>
+        <v>0.2441587223207942</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1459973372451062</v>
+        <v>-0.1267031595751486</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02313638394050577</v>
+        <v>-0.0494267734791603</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3901,76 +3901,76 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1086793530610886</v>
+        <v>0.04028797787418142</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01457340304247426</v>
+        <v>-0.03433169241180566</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1186343477652751</v>
+        <v>-0.06565285730679846</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03895121439654637</v>
+        <v>-0.05209454246195017</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.004741122020611612</v>
+        <v>-0.08964595868795341</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.013883691190485</v>
+        <v>-0.05737026178824835</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.006524039300323276</v>
+        <v>0.07523353762263071</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.06847549428556782</v>
+        <v>-0.06821674058408261</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.04773710363497279</v>
+        <v>0.03360621567634158</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3979,28 +3979,28 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4231111987577658</v>
+        <v>0.2222745332014238</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.031711669508504</v>
+        <v>-0.06945752934609975</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1277890467114842</v>
+        <v>-0.1194668099162634</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,25 +4009,25 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05429963440443489</v>
+        <v>-0.009542049507968138</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1518408726939688</v>
+        <v>-0.01945975804290244</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.09177743244540326</v>
+        <v>-0.01500006223738379</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,19 +4036,19 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.117803487947492</v>
+        <v>-0.003449372059106867</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06496233133081793</v>
+        <v>0.03705417189882539</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1911574122023108</v>
+        <v>0.05006449647120944</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
         <v>0</v>
@@ -4057,49 +4057,49 @@
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.152951210823048</v>
+        <v>0.1280762639663203</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01567412819619261</v>
+        <v>-0.08082038899565522</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.07107637473921107</v>
+        <v>-0.02659361723549905</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1076250023366904</v>
+        <v>-0.08075687331609734</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.002546727346841302</v>
+        <v>0.07205177568203684</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.01921448332050094</v>
+        <v>0.003941546891725749</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
@@ -4111,31 +4111,31 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.007675100576740992</v>
+        <v>-0.03823895014791587</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.101975651758632</v>
+        <v>0.1121371417850435</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.07509767032681681</v>
+        <v>0.01314846442727168</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>-0</v>
@@ -4144,22 +4144,22 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.07567149819929372</v>
+        <v>-0.08030937673327315</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.03673323044389321</v>
+        <v>0.07803708567215201</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02246260350475777</v>
+        <v>0.01132786992206351</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,16 +4171,16 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.04751250332531083</v>
+        <v>-0.04745147904470356</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.04924193059300066</v>
+        <v>0.01034499719553059</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03152932617327559</v>
+        <v>-0.02572530714429172</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4198,25 +4198,25 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.08717996725976607</v>
+        <v>-0.04751444776512426</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.006513801805190297</v>
+        <v>-0.01069529527476468</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.04421012813749089</v>
+        <v>-0.0308703816960606</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,16 +4225,16 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.09445239227633277</v>
+        <v>-0.001671533397271223</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.02056613163100841</v>
+        <v>0.04865448264155431</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01783563490712721</v>
+        <v>-0.0168421129138547</v>
       </c>
       <c r="EB7" t="n">
         <v>-0</v>
@@ -4246,85 +4246,85 @@
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.09540738897785693</v>
+        <v>-0.05081916366587213</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.01028015155231798</v>
+        <v>0.05442352561411274</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.05427200741381138</v>
+        <v>0.04386766587231176</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.005034602220195861</v>
+        <v>-0.03366750451551384</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.001329601286454684</v>
+        <v>0.0522362214871209</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.03568744617016151</v>
+        <v>-0.0006880467492531361</v>
       </c>
       <c r="ET7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0757012908168028</v>
+        <v>-0.08563145512221194</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0.008129331056488252</v>
+        <v>0.09293715371021044</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01058015164925317</v>
+        <v>-0.004973315799014191</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
@@ -4333,49 +4333,49 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.0621843637565723</v>
+        <v>0.08397723388932285</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.01226630649575794</v>
+        <v>0.06295212512267365</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.03044497742703797</v>
+        <v>0.001950860323043709</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05352508597917321</v>
+        <v>0.01835358290497112</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.00328797511613314</v>
+        <v>0.107013848119034</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.08749793075539372</v>
+        <v>-0.02600138501372071</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>-0</v>
@@ -4384,39 +4384,39 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.07371485920039135</v>
+        <v>-0.05110362570700401</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1389381326179158</v>
+        <v>0.0238378432792098</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.298155523377247</v>
+        <v>0.4232079089802486</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06206106127838192</v>
+        <v>0.01397905014612268</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1852685994213397</v>
+        <v>-0.3797404427702371</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2403770050812128</v>
+        <v>0.5597207658495565</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02684878583510969</v>
+        <v>-0.0877601414729685</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1533724520812653</v>
+        <v>-0.38420642536813</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04534761802832529</v>
+        <v>0.1004684542200344</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,40 +4479,40 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.05704212528152127</v>
+        <v>-0.1517535472367722</v>
       </c>
       <c r="X8" t="n">
-        <v>0.009080729783203302</v>
+        <v>-0.1254026199715162</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.002369820883845891</v>
+        <v>-0.08510729626987462</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01261164614090778</v>
+        <v>-0.3034058269421714</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.009821091536059302</v>
+        <v>0.07307556726872221</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4524,22 +4524,22 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.05604790590957734</v>
+        <v>0.1145915046393483</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02078031133041097</v>
+        <v>-0.08542858678905865</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.06052421966412333</v>
+        <v>-0.1410248201609111</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2357585318077677</v>
+        <v>0.729892087746348</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.05706086183833493</v>
+        <v>-0.3496420967073996</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1223579223620336</v>
+        <v>-0.3077703984054579</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.06909923009570129</v>
+        <v>-0.1047429380107797</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,52 +4587,52 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04512942638784316</v>
+        <v>0.01005909682244585</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.06534830866512532</v>
+        <v>-0.0663353650935353</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.07614411377211143</v>
+        <v>0.1646227972478003</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02063650787853983</v>
+        <v>0.1124057176850616</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.02623304052392049</v>
+        <v>0.1150103401382154</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1164263481080725</v>
+        <v>0.3201838536629217</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,37 +4641,37 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.04215525822093379</v>
+        <v>-0.04086962544002088</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.04603495067738177</v>
+        <v>-0.2639812386050845</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.05865819807587217</v>
+        <v>-0.1629635616167266</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.005931720797635378</v>
+        <v>0.04763362330607925</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.05929562418760954</v>
+        <v>0.1480643672732998</v>
       </c>
       <c r="CJ8" t="n">
         <v>-0</v>
@@ -4680,52 +4680,52 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.005846157274173099</v>
+        <v>-0.1863226508634481</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.005148199158540638</v>
+        <v>0.2188392067473652</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.04115847977149757</v>
+        <v>0.03579471146921953</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.05087568002114418</v>
+        <v>-0.1551452889667528</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.003958338450590107</v>
+        <v>0.03756822066236486</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.06290063068607926</v>
+        <v>0.1809944384464302</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -4734,25 +4734,25 @@
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.05894932196555932</v>
+        <v>-0.1519243141543897</v>
       </c>
       <c r="DG8" t="n">
         <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06110187667520923</v>
+        <v>-0.09438204230672485</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.003852959871399113</v>
+        <v>0.02738820945215707</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,13 +4761,13 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02472740377580921</v>
+        <v>-0.1032006314809398</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
@@ -4776,16 +4776,16 @@
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0109420766716275</v>
+        <v>0.007009884704089815</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.004256356648301668</v>
+        <v>0.201922762625991</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,46 +4794,46 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.05993310427873304</v>
+        <v>-0.0530484007763188</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.02922556145151545</v>
+        <v>0.08907973233473906</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.03399772431423871</v>
+        <v>0.03010913237480588</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.04709008219734419</v>
+        <v>-0.0714732353132084</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
         <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.008803377080850687</v>
+        <v>0.001068276544096561</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.06204987796296912</v>
+        <v>0.02249397243611118</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
@@ -4842,28 +4842,28 @@
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.03149441098002691</v>
+        <v>-0.05836812210043858</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.0257753046145599</v>
+        <v>-0.08627496546950546</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0.03196885046123576</v>
+        <v>-0.0536841434285398</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,61 +4875,61 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.05030630232549475</v>
+        <v>-0.1877839862356153</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.004381448937220327</v>
+        <v>0.009798171053744247</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.06127341526316506</v>
+        <v>0.150071627984233</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02137113376786219</v>
+        <v>0.1392038655129498</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.000121318485645493</v>
+        <v>-0.01655136094623389</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03184715723934108</v>
+        <v>0.1686533227491705</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.005951446581302453</v>
+        <v>0.09735598737294943</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,37 +4938,37 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.0428805526364039</v>
+        <v>-0.09338460903312849</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0340957589019014</v>
+        <v>-0.06663149553774105</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.007052604381150964</v>
+        <v>0.006429813502507063</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.02205001004132928</v>
+        <v>0.2149031902420609</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1517739155895729</v>
+        <v>0.3363155200215857</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,16 +4994,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04861522990302251</v>
+        <v>-0.009155915800165221</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1126526447279271</v>
+        <v>-0.1673451895137943</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1350754075090925</v>
+        <v>0.4065983743413993</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,16 +5021,16 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.03508759240094478</v>
+        <v>-0.1144442317849564</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.07855094673226355</v>
+        <v>-0.1653667878824806</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -5039,49 +5039,49 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01433379881775891</v>
+        <v>0.09220500230865648</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01455705370740886</v>
+        <v>-0.1308428087351101</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02324055623213817</v>
+        <v>-0.02891310475740042</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.01686803553471301</v>
+        <v>-0.04440790811736724</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01350250803941484</v>
+        <v>-0.2192757577669288</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.001617086878557437</v>
+        <v>0.05371070126328948</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5093,22 +5093,22 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01720789039650837</v>
+        <v>0.02294096259557263</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.02270279634494534</v>
+        <v>-0.05038615741887051</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.01105007190224198</v>
+        <v>0.007216785754831092</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5117,10 +5117,10 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.120994041971936</v>
+        <v>0.3910623276641072</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
@@ -5129,16 +5129,16 @@
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.03460643722679353</v>
+        <v>-0.2772408990004231</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.04245615848365781</v>
+        <v>-0.1668576987924457</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0457818576645847</v>
+        <v>-0.003518085774933072</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,13 +5156,13 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.03968324703385522</v>
+        <v>0.01446732877114955</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.06762148481346751</v>
+        <v>-0.05708226467189532</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
         <v>-0</v>
@@ -5171,37 +5171,37 @@
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.04817137729403159</v>
+        <v>0.05199367491723796</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02164728268419</v>
+        <v>0.08293756460630572</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.02456503844475974</v>
+        <v>-0.01479604464576694</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.05802326120663533</v>
+        <v>0.1837584916135507</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,52 +5210,52 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.00549449395626839</v>
+        <v>-0.06710765902037454</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.007497948843167415</v>
+        <v>-0.08166812369678919</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.02710216064061249</v>
+        <v>-0.11067382175033</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002883438412489826</v>
+        <v>0.02317577686358403</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.02899730859326392</v>
+        <v>0.06149578858528294</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.01969949111576472</v>
+        <v>-0.1074283605359569</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
@@ -5264,64 +5264,64 @@
         <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.008581365340144288</v>
+        <v>0.154577743692365</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.01866781142393886</v>
+        <v>0.1279522944188075</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.01999108563811709</v>
+        <v>-0.1123313828569275</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.005400182336710682</v>
+        <v>0.01473961655636684</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02948445110886235</v>
+        <v>0.08105866099970779</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03191763648372965</v>
+        <v>-0.04489155410054579</v>
       </c>
       <c r="DG9" t="n">
         <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.04147238320620589</v>
+        <v>-0.1724373802586241</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.005917143672262027</v>
+        <v>0.02926379717252621</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5336,76 +5336,76 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.01137114856477892</v>
+        <v>-0.01429019310295507</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.00833401786074117</v>
+        <v>-0.09356177800496863</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.01140950982976171</v>
+        <v>0.07098489639059351</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.04512858273684784</v>
+        <v>-0.006676073032105258</v>
       </c>
       <c r="DY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.02088367386711002</v>
+        <v>-0.03736737812639675</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.007675615296668074</v>
+        <v>0.02845261581748243</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.02749297540612856</v>
+        <v>-0.05612772648468442</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.005796075757422661</v>
+        <v>0.01834357541361846</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0346602825901107</v>
+        <v>0.006404822020641447</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5417,79 +5417,79 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.003617876034851138</v>
+        <v>-0.02141857446098784</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01596740373640434</v>
+        <v>0.005655988480918926</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0125587331836401</v>
+        <v>0.1201618364923911</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.02085266260591721</v>
+        <v>-0.1254222581948457</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.009411074163093605</v>
+        <v>-0.0006397615825679714</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0351260081730937</v>
+        <v>0.05323554298546797</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02431696723494228</v>
+        <v>0.1908726313932415</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.004578963124353846</v>
+        <v>-0.08069504136350431</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.01779031579575959</v>
+        <v>0.1369936955605715</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
@@ -5498,55 +5498,55 @@
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.008326910204402049</v>
+        <v>0.06889976760512119</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.02636988253532794</v>
+        <v>-0.1050718923760996</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.00827738434088381</v>
+        <v>-0.03288124870714133</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.00382869088613016</v>
+        <v>-0.03420563505549706</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.01297539771010067</v>
+        <v>0.08013579547270477</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,43 +5554,43 @@
         <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.5706246715725708</v>
+        <v>-0.5192700467589784</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3187756063171609</v>
+        <v>0.5248069792491289</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05215541092426699</v>
+        <v>0.2327520767764726</v>
       </c>
       <c r="F10" t="n">
         <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3857571640737584</v>
+        <v>-0.4890514132010519</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3385814277128879</v>
+        <v>0.6939063176669397</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0104357255454788</v>
+        <v>0.29010302733709</v>
       </c>
       <c r="O10" t="n">
         <v>-0</v>
@@ -5599,79 +5599,79 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.132844515621456</v>
+        <v>0.009884670848425425</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.07548170601269155</v>
+        <v>0.05736656504176688</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1001660871006488</v>
+        <v>0.08972847365025936</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.1608354579320231</v>
+        <v>-0.04743737715561325</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.06790214133515203</v>
+        <v>0.1143564771785901</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.03529300547267249</v>
+        <v>0.006955584629143871</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.09698693161024634</v>
+        <v>-0.2355501051625201</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.07661069873253433</v>
+        <v>0.05345236285813042</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.1481833273687627</v>
+        <v>-0.08808375657333742</v>
       </c>
       <c r="AP10" t="n">
         <v>-0</v>
@@ -5680,7 +5680,7 @@
         <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
         <v>-0</v>
@@ -5689,43 +5689,43 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.5352534342577875</v>
+        <v>-0.4958293442469757</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2378292021294334</v>
+        <v>0.1668274037768391</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1350315533034948</v>
+        <v>0.4167850538169033</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
         <v>-0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
         <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.04956950639722306</v>
+        <v>0.008071089395464113</v>
       </c>
       <c r="BE10" t="n">
         <v>-0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.005180354388690742</v>
+        <v>0.1333828226437742</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.127311007127852</v>
+        <v>0.01016399447055126</v>
       </c>
       <c r="BH10" t="n">
         <v>-0</v>
@@ -5734,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
         <v>-0</v>
@@ -5743,22 +5743,22 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.05350882629718057</v>
+        <v>-0.03724312675706869</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0.08999910112682026</v>
+        <v>-0.1596936990106908</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.1707330815733983</v>
+        <v>-0.03738746923555741</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS10" t="n">
         <v>0</v>
@@ -5770,16 +5770,16 @@
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.1472216603928065</v>
+        <v>-0.227380191849861</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.1419100379096563</v>
+        <v>0.2059867812459049</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.05369959713759118</v>
+        <v>0.07133107754977951</v>
       </c>
       <c r="BZ10" t="n">
         <v>-0</v>
@@ -5788,25 +5788,25 @@
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1140798690444197</v>
+        <v>0.2349687942389595</v>
       </c>
       <c r="CF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0.03606380300362672</v>
+        <v>-0.184408443740338</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.05168671064959512</v>
+        <v>-0.03819442710561707</v>
       </c>
       <c r="CI10" t="n">
         <v>0</v>
@@ -5818,79 +5818,79 @@
         <v>-0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.09060980826567323</v>
+        <v>0.1521726834898804</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.1191178597500975</v>
+        <v>-0.1921121391634407</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.05616965731260361</v>
+        <v>-0.1246831793321908</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1317999521744691</v>
+        <v>0.2193748911808043</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
       </c>
       <c r="CY10" t="n">
-        <v>-0.07129231610656096</v>
+        <v>-0.2052793452197826</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0379958548241271</v>
+        <v>-0.09301947049271202</v>
       </c>
       <c r="DA10" t="n">
         <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC10" t="n">
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0109352028121371</v>
+        <v>0.05073027488627944</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0.01130368195361407</v>
+        <v>0.0257187773589874</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.09818593517793399</v>
+        <v>0.01584964215747615</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5905,22 +5905,22 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.02999530032301195</v>
+        <v>0.1504025019694053</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.1252406333359355</v>
+        <v>-0.06803296064274866</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.08153276942027049</v>
+        <v>-0.01212699644090555</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
@@ -5932,25 +5932,25 @@
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.1579297165819579</v>
+        <v>0.06982294057893071</v>
       </c>
       <c r="DY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.00656569636797374</v>
+        <v>-0.05422597723988788</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.01613353566779456</v>
+        <v>-0.0475104811389914</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE10" t="n">
         <v>0</v>
@@ -5959,49 +5959,49 @@
         <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.04806705536977129</v>
+        <v>0.1787915539651769</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0.1079769520368439</v>
+        <v>-0.1632157080382618</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.006820668916142606</v>
+        <v>-0.08370510577542811</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.1736354900792432</v>
+        <v>0.1623468511353138</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.04035844732804725</v>
+        <v>0.1449854088930326</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.09913394204250914</v>
+        <v>0.01190010810592675</v>
       </c>
       <c r="ET10" t="n">
         <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
         <v>-0</v>
@@ -6013,106 +6013,106 @@
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.121948590806715</v>
+        <v>0.2561619034000555</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.04971711474863039</v>
+        <v>-0.2198647633587886</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.03450605831022793</v>
+        <v>-0.04770447619694954</v>
       </c>
       <c r="FC10" t="n">
         <v>0</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.09290107148814473</v>
+        <v>-0.0470551349115754</v>
       </c>
       <c r="FI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.09514164835308166</v>
+        <v>-0.1612907818554879</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.05833306165665017</v>
+        <v>-0.01113764868092162</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.02529672178500598</v>
+        <v>-0.08780024939729894</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.09985519983295854</v>
+        <v>-0.06808791647669531</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.004183057857940621</v>
+        <v>0.06713105906321643</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.007399995330741199</v>
+        <v>0.1275537100227525</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.1189097780430205</v>
+        <v>-0.1061840312089389</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE10" t="n">
         <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6692,25 +6692,25 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1829240012658347</v>
+        <v>0.4414282581601336</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1283719139014717</v>
+        <v>-0.0004576204746039414</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.04502705426087351</v>
+        <v>-0.1902842901121795</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.113984940696361</v>
+        <v>0.6363430635813241</v>
       </c>
       <c r="L12" t="n">
         <v>-0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1197142787959435</v>
+        <v>-0.1034181173273263</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.02684546242397043</v>
+        <v>-0.1066473063063357</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03246071399365046</v>
+        <v>0.1102107306266436</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
@@ -6755,52 +6755,52 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.01854596711954459</v>
+        <v>-0.07187979143231465</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0350581919629134</v>
+        <v>0.02833390473907414</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03269595470796838</v>
+        <v>-0.01469910347453011</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.02172288882983687</v>
+        <v>-0.2733039915859573</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.005178595632390185</v>
+        <v>-0.01747740607392911</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03326141600217759</v>
+        <v>0.1271503634140448</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
@@ -6809,13 +6809,13 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.02343667536253118</v>
+        <v>-0.06679376354760212</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.03068835400738558</v>
+        <v>-0.09714069920269983</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,106 +6824,106 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1514684067812839</v>
+        <v>0.540632284684372</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.05610574894186021</v>
+        <v>-0.2691471423586974</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.02371592146532917</v>
+        <v>-0.1507926830173043</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03555876810642063</v>
+        <v>-0.01877475952741584</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.06966282110222273</v>
+        <v>-0.07863968345887082</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.01166457448584459</v>
+        <v>-0.07799684201099903</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.07179274158320442</v>
+        <v>0.05296047606580116</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.04729761204742182</v>
+        <v>0.08921100217953021</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.02917785834003048</v>
+        <v>0.01711648530161288</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.08478793415477198</v>
+        <v>0.3004008019901804</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.03893853036098986</v>
+        <v>-0.06255975347929914</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.03229972794791468</v>
+        <v>-0.07467407820995717</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>-0</v>
@@ -6935,7 +6935,7 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.02916945979829338</v>
+        <v>-0.1381838584833815</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
@@ -6944,25 +6944,25 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.02001166747245502</v>
+        <v>0.0242128177419951</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.01658810555566378</v>
+        <v>0.07466603698998021</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01109836573607711</v>
+        <v>-0.2285381694702853</v>
       </c>
       <c r="CO12" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.008031443966080165</v>
+        <v>0.2467435112313654</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.03056631538903333</v>
+        <v>0.1077704946939264</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,58 +6983,58 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.01622067631753794</v>
+        <v>-0.1286316339476744</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.01567691146812417</v>
+        <v>-0.005606464015127697</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.02199240146198362</v>
+        <v>0.08842239550886134</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.03536507623607122</v>
+        <v>-0.06485642363220336</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04563534378137818</v>
+        <v>-0.08722282393046443</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.003354307469953589</v>
+        <v>0.05275613376636407</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.03060691648139703</v>
+        <v>-0.09390185649493581</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03597390562026358</v>
+        <v>-0.01286820522927833</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.03616295272945598</v>
+        <v>0.04033965534771535</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
@@ -7070,52 +7070,52 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.01570112277686396</v>
+        <v>0.07704021766501981</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.04661972562958131</v>
+        <v>-0.01346119936547603</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0.01990475912311146</v>
+        <v>0.0182716692575281</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.006895922316238825</v>
+        <v>-0.02184367439600543</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0187515651291781</v>
+        <v>-0.0357071037073741</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0.004160143040853005</v>
+        <v>0.003560900828379942</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,22 +7124,22 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.001805782706439358</v>
+        <v>-0.02235131920931331</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.01671338500626989</v>
+        <v>-0.1226536162210764</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0.04107314947991825</v>
+        <v>-0.1501634403155164</v>
       </c>
       <c r="EU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,7 +7151,7 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.01329199393964919</v>
+        <v>-0.1561313491250409</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
@@ -7160,13 +7160,13 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01422151433630041</v>
+        <v>-0.007466593929289857</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.02576750247698913</v>
+        <v>0.06873551253828629</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,61 +7178,61 @@
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02682640636682243</v>
+        <v>-0.1046362716673507</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03859081127150677</v>
+        <v>0.1268223014804346</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.007983269362963324</v>
+        <v>0.05168671801866122</v>
       </c>
       <c r="FM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.008438347296712957</v>
+        <v>0.01608602652452919</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.01392731353707457</v>
+        <v>-0.06449915969123372</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.02040919400154603</v>
+        <v>-0.04030157601384182</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.03206266536961964</v>
+        <v>-0.04853863131403331</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
@@ -7241,16 +7241,16 @@
         <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.01819437699495738</v>
+        <v>0.03681160732703978</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>0</v>
@@ -7258,46 +7258,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4795651153191581</v>
+        <v>0.09606356302028411</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1529771120485157</v>
+        <v>-0.2869397396562856</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1268987792104213</v>
+        <v>-0.04999150617464684</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.341031274811212</v>
+        <v>0.06384998780564587</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1626095738492312</v>
+        <v>-0.3578338979273083</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1956471445525756</v>
+        <v>-0.1031932793130349</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -7306,34 +7306,34 @@
         <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1417379232729527</v>
+        <v>0.08131996866809493</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.02423914358289279</v>
+        <v>-0.05033817650360733</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04758086288654551</v>
+        <v>-0.1073321346844814</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,79 +7342,79 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1486253476802301</v>
+        <v>-0.02970458107865039</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.06219665194812943</v>
+        <v>-0.0924045310163832</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01503442428114518</v>
+        <v>-0.1281022982826094</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.02521118813522076</v>
+        <v>0.1375326755443187</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.03714872537210029</v>
+        <v>-0.08583066561911043</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0798248553876872</v>
+        <v>0.02734955323573525</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4251063753434963</v>
+        <v>0.2237118003931955</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.05223720642321417</v>
+        <v>-0.1126880582229138</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1201759665396106</v>
+        <v>-0.3250179253540211</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
@@ -7423,16 +7423,16 @@
         <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.06263297992817574</v>
+        <v>-0.0912349821388798</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.08605793861645021</v>
+        <v>-0.05971169937252787</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.216115264594679</v>
+        <v>0.02874895836035704</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
         <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,22 +7450,22 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1819722555717474</v>
+        <v>0.09749893572198533</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.04882037029310953</v>
+        <v>0.07502137188703296</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1162433887670816</v>
+        <v>0.06681147544310416</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,43 +7477,43 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2275236402350448</v>
+        <v>0.1918504627710727</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.03951386362269742</v>
+        <v>-0.1567325544317312</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.05120169755981124</v>
+        <v>-0.1414879156853743</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.08375815196614528</v>
+        <v>-0.01242862798486229</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.005956518229861109</v>
+        <v>0.1579513646579104</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.006025072541400497</v>
+        <v>0.05540851394150083</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -7522,7 +7522,7 @@
         <v>-0</v>
       </c>
       <c r="CK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL13" t="n">
         <v>-0</v>
@@ -7531,16 +7531,16 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.1029585137820613</v>
+        <v>-0.08439543910079984</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.1233054632151755</v>
+        <v>0.2649879760504203</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.09274895826635121</v>
+        <v>0.2195226500623939</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
@@ -7549,58 +7549,58 @@
         <v>-0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.05385781666778221</v>
+        <v>0.007547114188094407</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.03158898384576402</v>
+        <v>0.177674179392312</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.004901155893951134</v>
+        <v>0.06441458096326139</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.08117667398080412</v>
+        <v>0.02263796402632002</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0.0005717402072404344</v>
+        <v>0.0309825137737323</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02306993971436003</v>
+        <v>-0.001174363667907032</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7612,43 +7612,43 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.07488767241930343</v>
+        <v>-0.05439147349130639</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0.06654675688611755</v>
+        <v>0.05577036256333628</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.007078702451923352</v>
+        <v>0.001108171216025912</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.04396684647622225</v>
+        <v>0.01370265308784211</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.03788225619744454</v>
+        <v>0.04206142938771635</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.0510579698227704</v>
+        <v>-0.118796795562562</v>
       </c>
       <c r="EB13" t="n">
         <v>0</v>
@@ -7657,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
@@ -7666,25 +7666,25 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.02867059293885357</v>
+        <v>0.05483952839630284</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.06589165377074194</v>
+        <v>0.150688347367382</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.06726729827058191</v>
+        <v>0.07081532882933261</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
@@ -7693,25 +7693,25 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.0568650862688481</v>
+        <v>-0.03378186013717065</v>
       </c>
       <c r="EQ13" t="n">
         <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0.06347514421775294</v>
+        <v>-0.1714229323024246</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.008766990974300656</v>
+        <v>0.02550715574891449</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW13" t="n">
         <v>-0</v>
@@ -7720,70 +7720,70 @@
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.06261309896965866</v>
+        <v>-0.01852776988686233</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.02194651345258754</v>
+        <v>0.1860184287386595</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.01525298015115072</v>
+        <v>0.05590157299616644</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF13" t="n">
         <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.05002456524392598</v>
+        <v>0.02227607643341189</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.05896961693994668</v>
+        <v>0.03860570305951027</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.05174648615924526</v>
+        <v>-0.05880671362687474</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM13" t="n">
         <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.02747275430736851</v>
+        <v>-0.005019414168564116</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0.02734220972481204</v>
+        <v>0.1329214533177314</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.02335604045352977</v>
+        <v>-0.09155205249289153</v>
       </c>
       <c r="FU13" t="n">
         <v>-0</v>
@@ -7795,34 +7795,34 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
         <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02139667401806706</v>
+        <v>-0.03184374367634193</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.0451821983446661</v>
+        <v>0.129963695476913</v>
       </c>
       <c r="GC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
